--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAgeDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAgeDetail.xlsx
@@ -97,7 +97,7 @@
     <t>{.date}</t>
   </si>
   <si>
-    <t>{.avgInventoryAgeDays}</t>
+    <t>{.avgInventoryAgeDaysStr}</t>
   </si>
   <si>
     <t>{.transactionNo}</t>
